--- a/Program/Datos/datos_manuales.xlsx
+++ b/Program/Datos/datos_manuales.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mhoyosme\Desktop\Proyecto\Program\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E05D5C-E27D-4781-B035-DCD2361B45DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9A74FB-8ED7-4178-AEEB-1F843A58B2F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{CD6D87B3-3E85-4D9D-BFF0-D4E802493E81}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="info_nodo" sheetId="1" r:id="rId1"/>
     <sheet name="inventario_ac" sheetId="2" r:id="rId2"/>
     <sheet name="inventario_pdb" sheetId="3" r:id="rId3"/>
+    <sheet name="inventario_racks" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="181">
   <si>
     <t>75.0</t>
   </si>
@@ -347,6 +348,240 @@
   </si>
   <si>
     <t>ubicacion</t>
+  </si>
+  <si>
+    <t>nombre_rack</t>
+  </si>
+  <si>
+    <t>u_totales</t>
+  </si>
+  <si>
+    <t>u_ocupadas_listado</t>
+  </si>
+  <si>
+    <t>u_libres_listado</t>
+  </si>
+  <si>
+    <t>nombre_foto</t>
+  </si>
+  <si>
+    <t>Detalle_rack</t>
+  </si>
+  <si>
+    <t>CLO-IDO-01-R1</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>NOKIA-S7210-SAS-SX-01-02-RACK1</t>
+  </si>
+  <si>
+    <t>fila1_Rack1.jpg</t>
+  </si>
+  <si>
+    <t>CLO-IDO-01-R2</t>
+  </si>
+  <si>
+    <t>CLO-IDO-01-R3</t>
+  </si>
+  <si>
+    <t>CLO-IDO-01-R4</t>
+  </si>
+  <si>
+    <t>01-RACK1.xlsx</t>
+  </si>
+  <si>
+    <t>CLO-IDO-02-R1</t>
+  </si>
+  <si>
+    <t>CLO-IDO-02-R2</t>
+  </si>
+  <si>
+    <t>CLO-IDO-02-R3</t>
+  </si>
+  <si>
+    <t>CLO-IDO-02-R4</t>
+  </si>
+  <si>
+    <t>CLO-IDO-02-R5</t>
+  </si>
+  <si>
+    <t>CLO-IDO-02-R6</t>
+  </si>
+  <si>
+    <t>CLO-IDO-02-R7</t>
+  </si>
+  <si>
+    <t>CLO-IDO-02-R8</t>
+  </si>
+  <si>
+    <t>GPX147-R2-RA2-STX-F1-R2-ODF</t>
+  </si>
+  <si>
+    <t>ODF-CCI-CCIDCLO-OLT01-H</t>
+  </si>
+  <si>
+    <t>CCIDCLO-OLT01-CCI</t>
+  </si>
+  <si>
+    <t>RACK1</t>
+  </si>
+  <si>
+    <t>RACK2</t>
+  </si>
+  <si>
+    <t>RACK3</t>
+  </si>
+  <si>
+    <t>RACK6</t>
+  </si>
+  <si>
+    <t>RACK7</t>
+  </si>
+  <si>
+    <t>RACK8</t>
+  </si>
+  <si>
+    <t>01-RACK2.xlsx</t>
+  </si>
+  <si>
+    <t>02-RACK2.xlsx</t>
+  </si>
+  <si>
+    <t>01-RACK3.xlsx</t>
+  </si>
+  <si>
+    <t>02-RACK1.xlsx</t>
+  </si>
+  <si>
+    <t>02-RACK3.xlsx</t>
+  </si>
+  <si>
+    <t>02-RACK4.xlsx</t>
+  </si>
+  <si>
+    <t>02-RACK6.xlsx</t>
+  </si>
+  <si>
+    <t>02-RACK7.xlsx</t>
+  </si>
+  <si>
+    <t>01-RACK4.xlsx</t>
+  </si>
+  <si>
+    <t>fila1_Rack2.jpg</t>
+  </si>
+  <si>
+    <t>fila2_Rack2.jpg</t>
+  </si>
+  <si>
+    <t>fila1_Rack3.jpg</t>
+  </si>
+  <si>
+    <t>fila1_Rack4.jpg</t>
+  </si>
+  <si>
+    <t>fila2_Rack1.jpg</t>
+  </si>
+  <si>
+    <t>fila2_Rack3.jpg</t>
+  </si>
+  <si>
+    <t>fila2_Rack4.jpg</t>
+  </si>
+  <si>
+    <t>fila2_Rack6.jpg</t>
+  </si>
+  <si>
+    <t>fila2_Rack7.jpg</t>
+  </si>
+  <si>
+    <t>fila2_Rack5.jpg</t>
+  </si>
+  <si>
+    <t>fila2_Rack8.jpg</t>
+  </si>
+  <si>
+    <t>1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24</t>
+  </si>
+  <si>
+    <t>24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44</t>
+  </si>
+  <si>
+    <t>1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23</t>
+  </si>
+  <si>
+    <t>40, 41, 42, 43, 44, 45</t>
+  </si>
+  <si>
+    <t>1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39</t>
+  </si>
+  <si>
+    <t>Disponible</t>
+  </si>
+  <si>
+    <t>Vacio</t>
+  </si>
+  <si>
+    <t>Espacio</t>
+  </si>
+  <si>
+    <t>3, 4, 5, 6, 7, 8, 9, 10, 11</t>
+  </si>
+  <si>
+    <t>1, 2, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46</t>
+  </si>
+  <si>
+    <t>1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 42, 43, 44</t>
+  </si>
+  <si>
+    <t>15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41</t>
+  </si>
+  <si>
+    <t>1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45</t>
+  </si>
+  <si>
+    <t>17, 18, 19, 20, 21, 22, 23</t>
+  </si>
+  <si>
+    <t>3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45</t>
+  </si>
+  <si>
+    <t>1, 2</t>
+  </si>
+  <si>
+    <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45</t>
+  </si>
+  <si>
+    <t>1, 2, 3, 4, 5, 6, 7, 8, 9, 30, 31, 32, 33, 34</t>
+  </si>
+  <si>
+    <t>1, 2, 3, 4, 42, 43, 44, 45</t>
+  </si>
+  <si>
+    <t>5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41</t>
+  </si>
+  <si>
+    <t>25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45</t>
+  </si>
+  <si>
+    <t>RACK5-ODF</t>
+  </si>
+  <si>
+    <t>RACK4-ODF</t>
+  </si>
+  <si>
+    <t>1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45</t>
+  </si>
+  <si>
+    <t>17, 18, 19, 20, 21, 22, 23, 24, 25, 26</t>
+  </si>
+  <si>
+    <t>21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45</t>
+  </si>
+  <si>
+    <t>1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20</t>
   </si>
 </sst>
 </file>
@@ -459,7 +694,37 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="39">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -850,47 +1115,64 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5874A6EA-08E4-4C13-B67C-CB816184D3C0}" name="Tabla2" displayName="Tabla2" ref="A1:G2" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5874A6EA-08E4-4C13-B67C-CB816184D3C0}" name="Tabla2" displayName="Tabla2" ref="A1:G2" totalsRowShown="0" headerRowDxfId="38" dataDxfId="36" headerRowBorderDxfId="37" tableBorderDxfId="35" totalsRowBorderDxfId="34">
   <autoFilter ref="A1:G2" xr:uid="{5874A6EA-08E4-4C13-B67C-CB816184D3C0}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{9F2439FA-30A1-4D90-9F47-A866995AD462}" name="nombre_nodo" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{E1FDA295-F988-4715-B9C7-42286712743D}" name="tipo" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{E955F37D-B353-4F7A-9521-F49CF205229C}" name="codigo" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{22F231D9-9879-4122-9BAF-253B8C04BB15}" name="regional" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{CA56A5C1-DCFB-45F9-A91D-E19FDCFDDF4C}" name="direccion" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{42241B89-6C4C-4F8D-8BF0-C33F36C93C1D}" name="capacidad_kva" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{96DBA14E-72BF-4616-A90F-5169ACCA998C}" name="voltaje_sistema_dc" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{9F2439FA-30A1-4D90-9F47-A866995AD462}" name="nombre_nodo" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{E1FDA295-F988-4715-B9C7-42286712743D}" name="tipo" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{E955F37D-B353-4F7A-9521-F49CF205229C}" name="codigo" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{22F231D9-9879-4122-9BAF-253B8C04BB15}" name="regional" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{CA56A5C1-DCFB-45F9-A91D-E19FDCFDDF4C}" name="direccion" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{42241B89-6C4C-4F8D-8BF0-C33F36C93C1D}" name="capacidad_kva" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{96DBA14E-72BF-4616-A90F-5169ACCA998C}" name="voltaje_sistema_dc" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2E5421E9-2724-423C-851B-A0845D404EE3}" name="Tabla3" displayName="Tabla3" ref="A1:F5" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2E5421E9-2724-423C-851B-A0845D404EE3}" name="Tabla3" displayName="Tabla3" ref="A1:F5" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
   <autoFilter ref="A1:F5" xr:uid="{2E5421E9-2724-423C-851B-A0845D404EE3}"/>
   <tableColumns count="6">
-    <tableColumn id="7" xr3:uid="{4DA03894-7D07-44E5-BB0D-94373ECA9338}" name="ubicacion" dataDxfId="14"/>
-    <tableColumn id="1" xr3:uid="{FEF86DC1-CDF6-4D2B-9711-3CE2E8FDC61D}" name="componente" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{E8898F3B-F793-4C03-9ADB-3E0756FDECAF}" name="marca" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{E4F60FA1-A5C6-4AC3-BF15-A364399D1E4E}" name="referencia" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{CD65DA30-5B1A-4E7C-8023-7B23F0D22BDF}" name="capacidad_amps" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{00B2E6A4-9D0B-4CA9-A4F2-C6F8CCF0A7FC}" name="calibre_cable" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{4DA03894-7D07-44E5-BB0D-94373ECA9338}" name="ubicacion" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{FEF86DC1-CDF6-4D2B-9711-3CE2E8FDC61D}" name="componente" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{E8898F3B-F793-4C03-9ADB-3E0756FDECAF}" name="marca" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{E4F60FA1-A5C6-4AC3-BF15-A364399D1E4E}" name="referencia" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{CD65DA30-5B1A-4E7C-8023-7B23F0D22BDF}" name="capacidad_amps" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{00B2E6A4-9D0B-4CA9-A4F2-C6F8CCF0A7FC}" name="calibre_cable" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4F279930-8CE0-4458-A500-A4804307D033}" name="Tabla4" displayName="Tabla4" ref="A1:G95" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4F279930-8CE0-4458-A500-A4804307D033}" name="Tabla4" displayName="Tabla4" ref="A1:G95" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <autoFilter ref="A1:G95" xr:uid="{4F279930-8CE0-4458-A500-A4804307D033}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{6CBBC484-43B4-4212-8A72-72C36A0AA59A}" name="pdb_nombre" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{E0A6FC31-B215-4C57-B8C0-A8E53A5B832B}" name="fuente" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{4F3E6BCE-4115-4327-9F4D-9FE1AB222BE1}" name="posicion" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{0F488469-BA24-4436-842B-6D2F9F8F4214}" name="estado" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{DAED4AB6-F7E7-4C43-9177-F8900C29D95C}" name="capacidad" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{59F7B2D4-6A80-447C-B8ED-E0F301A44C2C}" name="corriente" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{DCE97B5A-FEBD-4BAD-9EB4-7754B346D6AB}" name="equipo_refencia" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{6CBBC484-43B4-4212-8A72-72C36A0AA59A}" name="pdb_nombre" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{E0A6FC31-B215-4C57-B8C0-A8E53A5B832B}" name="fuente" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{4F3E6BCE-4115-4327-9F4D-9FE1AB222BE1}" name="posicion" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{0F488469-BA24-4436-842B-6D2F9F8F4214}" name="estado" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{DAED4AB6-F7E7-4C43-9177-F8900C29D95C}" name="capacidad" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{59F7B2D4-6A80-447C-B8ED-E0F301A44C2C}" name="corriente" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{DCE97B5A-FEBD-4BAD-9EB4-7754B346D6AB}" name="equipo_refencia" dataDxfId="10"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DE2280A1-9E4C-4DCD-BF7E-888FBA537ECA}" name="Tabla1" displayName="Tabla1" ref="A1:H13" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowCellStyle="Normal" dataCellStyle="Normal">
+  <autoFilter ref="A1:H13" xr:uid="{DE2280A1-9E4C-4DCD-BF7E-888FBA537ECA}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{3AB90701-9B35-41AA-99FD-EA000C0FBAC6}" name="nombre_rack" dataDxfId="7" dataCellStyle="Normal"/>
+    <tableColumn id="10" xr3:uid="{552625CA-FFA9-4D0F-9AE4-8E8AA2CFD81A}" name="Label" dataDxfId="6" dataCellStyle="Normal"/>
+    <tableColumn id="4" xr3:uid="{4E5A4E54-6DE7-48C8-8A66-7C97E2FA04A1}" name="u_totales" dataDxfId="5" dataCellStyle="Normal"/>
+    <tableColumn id="11" xr3:uid="{BE625927-AF15-478E-87C9-1BC144738D1C}" name="Espacio" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{D32C66C7-BCD4-4610-8774-1CC22DE4F9A0}" name="u_ocupadas_listado" dataDxfId="3" dataCellStyle="Normal"/>
+    <tableColumn id="6" xr3:uid="{282C4EE8-ED53-4C8B-B914-B33DF7A75E4D}" name="u_libres_listado" dataDxfId="2" dataCellStyle="Normal"/>
+    <tableColumn id="7" xr3:uid="{D325EA4D-3855-4FB8-8337-3E9BBFFDA68B}" name="nombre_foto" dataDxfId="1" dataCellStyle="Normal"/>
+    <tableColumn id="8" xr3:uid="{94BF02C2-1F70-4B1B-94F9-F73DDBFA1E1A}" name="Detalle_rack" dataDxfId="0" dataCellStyle="Normal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2255,6 +2537,9 @@
       <c r="E37" s="1">
         <v>10</v>
       </c>
+      <c r="F37" s="1">
+        <v>0</v>
+      </c>
       <c r="G37" s="1" t="s">
         <v>57</v>
       </c>
@@ -2275,6 +2560,9 @@
       <c r="E38" s="1">
         <v>100</v>
       </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
       <c r="G38" s="1" t="s">
         <v>58</v>
       </c>
@@ -2295,6 +2583,9 @@
       <c r="E39" s="1">
         <v>100</v>
       </c>
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
       <c r="G39" s="1" t="s">
         <v>71</v>
       </c>
@@ -2407,6 +2698,9 @@
       <c r="E44" s="1">
         <v>10</v>
       </c>
+      <c r="F44" s="1">
+        <v>0</v>
+      </c>
       <c r="G44" s="5" t="s">
         <v>76</v>
       </c>
@@ -2427,6 +2721,9 @@
       <c r="E45" s="1">
         <v>10</v>
       </c>
+      <c r="F45" s="1">
+        <v>0</v>
+      </c>
       <c r="G45" s="5" t="s">
         <v>77</v>
       </c>
@@ -2447,6 +2744,9 @@
       <c r="E46" s="1">
         <v>10</v>
       </c>
+      <c r="F46" s="1">
+        <v>0</v>
+      </c>
       <c r="G46" s="5" t="s">
         <v>78</v>
       </c>
@@ -2996,6 +3296,9 @@
       <c r="E70" s="1">
         <v>10</v>
       </c>
+      <c r="F70" s="1">
+        <v>0</v>
+      </c>
       <c r="G70" s="5" t="s">
         <v>79</v>
       </c>
@@ -3016,6 +3319,9 @@
       <c r="E71" s="1">
         <v>10</v>
       </c>
+      <c r="F71" s="1">
+        <v>0</v>
+      </c>
       <c r="G71" s="5" t="s">
         <v>80</v>
       </c>
@@ -3035,6 +3341,9 @@
       </c>
       <c r="E72" s="1">
         <v>10</v>
+      </c>
+      <c r="F72" s="1">
+        <v>0</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>81</v>
@@ -3576,4 +3885,359 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE8F478C-E72B-4135-8430-D9D1D7FC2E5F}">
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="119.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="106.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" s="1">
+        <v>44</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="1">
+        <v>45</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="1">
+        <v>46</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="1">
+        <v>44</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="1">
+        <v>45</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="1">
+        <v>45</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="1">
+        <v>45</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="1">
+        <v>45</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C10" s="1">
+        <v>45</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="1">
+        <v>45</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="1">
+        <v>45</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H13" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Program/Datos/datos_manuales.xlsx
+++ b/Program/Datos/datos_manuales.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mhoyosme\Desktop\Proyecto\Program\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9A74FB-8ED7-4178-AEEB-1F843A58B2F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D62192-68A2-48DB-9119-0E82294732E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{CD6D87B3-3E85-4D9D-BFF0-D4E802493E81}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{CD6D87B3-3E85-4D9D-BFF0-D4E802493E81}"/>
   </bookViews>
   <sheets>
     <sheet name="info_nodo" sheetId="1" r:id="rId1"/>
-    <sheet name="inventario_ac" sheetId="2" r:id="rId2"/>
+    <sheet name="protecciones" sheetId="2" r:id="rId2"/>
     <sheet name="inventario_pdb" sheetId="3" r:id="rId3"/>
     <sheet name="inventario_racks" sheetId="4" r:id="rId4"/>
   </sheets>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="196">
   <si>
     <t>75.0</t>
   </si>
@@ -89,9 +89,6 @@
     <t>NXM-250S/3300</t>
   </si>
   <si>
-    <t>4/0 AWG</t>
-  </si>
-  <si>
     <t>Totalizador ML</t>
   </si>
   <si>
@@ -101,9 +98,6 @@
     <t>NM1-125S/3300</t>
   </si>
   <si>
-    <t>1/0 AWG</t>
-  </si>
-  <si>
     <t>Breaker Rect 1</t>
   </si>
   <si>
@@ -326,9 +320,6 @@
     <t>capacidad_amps</t>
   </si>
   <si>
-    <t>calibre_cable</t>
-  </si>
-  <si>
     <t>fuente</t>
   </si>
   <si>
@@ -582,6 +573,60 @@
   </si>
   <si>
     <t>1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20</t>
+  </si>
+  <si>
+    <t>Schneider Electric</t>
+  </si>
+  <si>
+    <t>EasyPact EZC250N</t>
+  </si>
+  <si>
+    <t>calibre_cable_awg</t>
+  </si>
+  <si>
+    <t>4/0</t>
+  </si>
+  <si>
+    <t>1/0</t>
+  </si>
+  <si>
+    <t>Totalizador Fuente A</t>
+  </si>
+  <si>
+    <t>Totalizador Fuente B</t>
+  </si>
+  <si>
+    <t>EasyPact EZC250F</t>
+  </si>
+  <si>
+    <t>Contactor Red</t>
+  </si>
+  <si>
+    <t>Contactor Generador</t>
+  </si>
+  <si>
+    <t>ABB</t>
+  </si>
+  <si>
+    <t>AF265‑30</t>
+  </si>
+  <si>
+    <t>Bussmann</t>
+  </si>
+  <si>
+    <t>NH3</t>
+  </si>
+  <si>
+    <t>Fusible PDB1 A</t>
+  </si>
+  <si>
+    <t>Fusible PDB2 A</t>
+  </si>
+  <si>
+    <t>Fusible PDB1 B</t>
+  </si>
+  <si>
+    <t>Fusible PDB2 B</t>
   </si>
 </sst>
 </file>
@@ -1131,15 +1176,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2E5421E9-2724-423C-851B-A0845D404EE3}" name="Tabla3" displayName="Tabla3" ref="A1:F5" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
-  <autoFilter ref="A1:F5" xr:uid="{2E5421E9-2724-423C-851B-A0845D404EE3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2E5421E9-2724-423C-851B-A0845D404EE3}" name="Tabla3" displayName="Tabla3" ref="A1:F15" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
+  <autoFilter ref="A1:F15" xr:uid="{2E5421E9-2724-423C-851B-A0845D404EE3}"/>
   <tableColumns count="6">
     <tableColumn id="7" xr3:uid="{4DA03894-7D07-44E5-BB0D-94373ECA9338}" name="ubicacion" dataDxfId="24"/>
     <tableColumn id="1" xr3:uid="{FEF86DC1-CDF6-4D2B-9711-3CE2E8FDC61D}" name="componente" dataDxfId="23"/>
     <tableColumn id="2" xr3:uid="{E8898F3B-F793-4C03-9ADB-3E0756FDECAF}" name="marca" dataDxfId="22"/>
     <tableColumn id="3" xr3:uid="{E4F60FA1-A5C6-4AC3-BF15-A364399D1E4E}" name="referencia" dataDxfId="21"/>
     <tableColumn id="4" xr3:uid="{CD65DA30-5B1A-4E7C-8023-7B23F0D22BDF}" name="capacidad_amps" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{00B2E6A4-9D0B-4CA9-A4F2-C6F8CCF0A7FC}" name="calibre_cable" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{00B2E6A4-9D0B-4CA9-A4F2-C6F8CCF0A7FC}" name="calibre_cable_awg" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1508,7 +1553,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>5</v>
@@ -1520,13 +1565,13 @@
         <v>9</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1562,7 +1607,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70FE85F0-6249-49C0-98C3-75140ABDEF17}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.85546875" customWidth="1"/>
@@ -1570,32 +1615,32 @@
     <col min="3" max="3" width="17.140625" customWidth="1"/>
     <col min="4" max="4" width="23.42578125" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>95</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>13</v>
@@ -1610,65 +1655,267 @@
         <v>200</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>186</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>188</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>189</v>
       </c>
       <c r="E3" s="1">
-        <v>225</v>
-      </c>
-      <c r="F3" s="1"/>
+        <v>400</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>188</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="E4" s="1">
-        <v>125</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>20</v>
+        <v>400</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="1">
+        <v>225</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="1">
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="1">
         <v>125</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F6" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="1">
+        <v>125</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E8" s="1">
+        <v>500</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E9" s="1">
+        <v>500</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E10" s="1">
+        <v>500</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E11" s="1">
+        <v>500</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E12" s="1">
+        <v>150</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E13" s="1">
+        <v>150</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E14" s="1">
+        <v>250</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E15" s="1">
+        <v>250</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1695,25 +1942,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1733,10 +1980,10 @@
         <v>80</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1756,15 +2003,15 @@
         <v>6</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
@@ -1779,15 +2026,15 @@
         <v>6</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
@@ -1802,15 +2049,15 @@
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>3</v>
@@ -1825,15 +2072,15 @@
         <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>3</v>
@@ -1851,12 +2098,12 @@
         <v>23</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>3</v>
@@ -1871,15 +2118,15 @@
         <v>100</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>3</v>
@@ -1894,15 +2141,15 @@
         <v>10</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>3</v>
@@ -1917,15 +2164,15 @@
         <v>10</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>3</v>
@@ -1940,15 +2187,15 @@
         <v>10</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>3</v>
@@ -1963,15 +2210,15 @@
         <v>10</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>3</v>
@@ -1986,15 +2233,15 @@
         <v>10</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>3</v>
@@ -2009,15 +2256,15 @@
         <v>63</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>3</v>
@@ -2032,15 +2279,15 @@
         <v>10</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>3</v>
@@ -2055,15 +2302,15 @@
         <v>10</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>3</v>
@@ -2081,12 +2328,12 @@
         <v>25</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>3</v>
@@ -2104,12 +2351,12 @@
         <v>14</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>3</v>
@@ -2124,15 +2371,15 @@
         <v>6</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>3</v>
@@ -2147,15 +2394,15 @@
         <v>6</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>3</v>
@@ -2164,7 +2411,7 @@
         <v>20</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E21" s="1">
         <v>0</v>
@@ -2173,12 +2420,12 @@
         <v>0</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>3</v>
@@ -2187,7 +2434,7 @@
         <v>21</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E22" s="1">
         <v>0</v>
@@ -2196,15 +2443,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C23" s="1">
         <v>1</v>
@@ -2216,18 +2463,18 @@
         <v>80</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C24" s="1">
         <v>2</v>
@@ -2239,18 +2486,18 @@
         <v>6</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C25" s="1">
         <v>3</v>
@@ -2262,18 +2509,18 @@
         <v>6</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C26" s="1">
         <v>4</v>
@@ -2285,18 +2532,18 @@
         <v>16</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C27" s="1">
         <v>5</v>
@@ -2308,18 +2555,18 @@
         <v>16</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C28" s="1">
         <v>6</v>
@@ -2334,15 +2581,15 @@
         <v>23</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C29" s="1">
         <v>7</v>
@@ -2354,18 +2601,18 @@
         <v>100</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C30" s="1">
         <v>8</v>
@@ -2377,18 +2624,18 @@
         <v>10</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C31" s="1">
         <v>9</v>
@@ -2400,18 +2647,18 @@
         <v>10</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C32" s="1">
         <v>10</v>
@@ -2423,18 +2670,18 @@
         <v>10</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C33" s="1">
         <v>11</v>
@@ -2446,18 +2693,18 @@
         <v>10</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C34" s="1">
         <v>12</v>
@@ -2469,18 +2716,18 @@
         <v>10</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C35" s="1">
         <v>13</v>
@@ -2492,18 +2739,18 @@
         <v>63</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C36" s="1">
         <v>14</v>
@@ -2515,18 +2762,18 @@
         <v>10</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C37" s="1">
         <v>15</v>
@@ -2541,15 +2788,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C38" s="1">
         <v>16</v>
@@ -2564,15 +2811,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C39" s="1">
         <v>17</v>
@@ -2587,15 +2834,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C40" s="1">
         <v>18</v>
@@ -2607,18 +2854,18 @@
         <v>6</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C41" s="1">
         <v>19</v>
@@ -2633,21 +2880,21 @@
         <v>14</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C42" s="1">
         <v>20</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E42" s="1">
         <v>0</v>
@@ -2656,21 +2903,21 @@
         <v>14</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C43" s="1">
         <v>21</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E43" s="1">
         <v>0</v>
@@ -2679,12 +2926,12 @@
         <v>0</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>3</v>
@@ -2702,12 +2949,12 @@
         <v>0</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>3</v>
@@ -2725,12 +2972,12 @@
         <v>0</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>3</v>
@@ -2748,12 +2995,12 @@
         <v>0</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>3</v>
@@ -2762,7 +3009,7 @@
         <v>4</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E47" s="1">
         <v>0</v>
@@ -2771,12 +3018,12 @@
         <v>0</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>3</v>
@@ -2785,7 +3032,7 @@
         <v>5</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E48" s="1">
         <v>0</v>
@@ -2794,12 +3041,12 @@
         <v>0</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>3</v>
@@ -2808,7 +3055,7 @@
         <v>6</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E49" s="1">
         <v>0</v>
@@ -2817,12 +3064,12 @@
         <v>0</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>3</v>
@@ -2831,7 +3078,7 @@
         <v>7</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E50" s="1">
         <v>0</v>
@@ -2840,12 +3087,12 @@
         <v>0</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>3</v>
@@ -2854,7 +3101,7 @@
         <v>8</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E51" s="1">
         <v>0</v>
@@ -2863,12 +3110,12 @@
         <v>0</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>3</v>
@@ -2877,7 +3124,7 @@
         <v>9</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E52" s="1">
         <v>0</v>
@@ -2886,12 +3133,12 @@
         <v>0</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>3</v>
@@ -2900,7 +3147,7 @@
         <v>10</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E53" s="1">
         <v>0</v>
@@ -2909,12 +3156,12 @@
         <v>0</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>3</v>
@@ -2923,7 +3170,7 @@
         <v>11</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E54" s="1">
         <v>0</v>
@@ -2932,12 +3179,12 @@
         <v>0</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>3</v>
@@ -2946,7 +3193,7 @@
         <v>12</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E55" s="1">
         <v>0</v>
@@ -2955,12 +3202,12 @@
         <v>0</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>3</v>
@@ -2969,7 +3216,7 @@
         <v>13</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E56" s="1">
         <v>0</v>
@@ -2978,12 +3225,12 @@
         <v>0</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>3</v>
@@ -2992,7 +3239,7 @@
         <v>14</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E57" s="1">
         <v>0</v>
@@ -3001,12 +3248,12 @@
         <v>0</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>3</v>
@@ -3015,7 +3262,7 @@
         <v>15</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E58" s="1">
         <v>0</v>
@@ -3024,12 +3271,12 @@
         <v>0</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>3</v>
@@ -3038,7 +3285,7 @@
         <v>16</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
@@ -3047,12 +3294,12 @@
         <v>0</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>3</v>
@@ -3061,7 +3308,7 @@
         <v>17</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
@@ -3070,12 +3317,12 @@
         <v>0</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>3</v>
@@ -3084,7 +3331,7 @@
         <v>18</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
@@ -3093,12 +3340,12 @@
         <v>0</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>3</v>
@@ -3107,7 +3354,7 @@
         <v>19</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E62" s="1">
         <v>0</v>
@@ -3116,12 +3363,12 @@
         <v>0</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>3</v>
@@ -3130,7 +3377,7 @@
         <v>20</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
@@ -3139,12 +3386,12 @@
         <v>0</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>3</v>
@@ -3153,7 +3400,7 @@
         <v>21</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E64" s="1">
         <v>0</v>
@@ -3162,12 +3409,12 @@
         <v>0</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>3</v>
@@ -3176,7 +3423,7 @@
         <v>22</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E65" s="1">
         <v>0</v>
@@ -3185,12 +3432,12 @@
         <v>0</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>3</v>
@@ -3199,7 +3446,7 @@
         <v>23</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E66" s="1">
         <v>0</v>
@@ -3208,12 +3455,12 @@
         <v>0</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>3</v>
@@ -3222,7 +3469,7 @@
         <v>24</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E67" s="1">
         <v>0</v>
@@ -3231,12 +3478,12 @@
         <v>0</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>3</v>
@@ -3245,7 +3492,7 @@
         <v>25</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E68" s="1">
         <v>0</v>
@@ -3254,12 +3501,12 @@
         <v>0</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>3</v>
@@ -3268,7 +3515,7 @@
         <v>26</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E69" s="1">
         <v>0</v>
@@ -3277,15 +3524,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C70" s="1">
         <v>1</v>
@@ -3300,15 +3547,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C71" s="1">
         <v>2</v>
@@ -3323,15 +3570,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C72" s="1">
         <v>3</v>
@@ -3346,21 +3593,21 @@
         <v>0</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C73" s="1">
         <v>4</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E73" s="1">
         <v>0</v>
@@ -3369,21 +3616,21 @@
         <v>0</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C74" s="1">
         <v>5</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E74" s="1">
         <v>0</v>
@@ -3392,21 +3639,21 @@
         <v>0</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C75" s="1">
         <v>6</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E75" s="1">
         <v>0</v>
@@ -3415,21 +3662,21 @@
         <v>0</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C76" s="1">
         <v>7</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E76" s="1">
         <v>0</v>
@@ -3438,21 +3685,21 @@
         <v>0</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C77" s="1">
         <v>8</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E77" s="1">
         <v>0</v>
@@ -3461,21 +3708,21 @@
         <v>0</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C78" s="1">
         <v>9</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E78" s="1">
         <v>0</v>
@@ -3484,21 +3731,21 @@
         <v>0</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C79" s="1">
         <v>10</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E79" s="1">
         <v>0</v>
@@ -3507,21 +3754,21 @@
         <v>0</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C80" s="1">
         <v>11</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E80" s="1">
         <v>0</v>
@@ -3530,21 +3777,21 @@
         <v>0</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C81" s="1">
         <v>12</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E81" s="1">
         <v>0</v>
@@ -3553,21 +3800,21 @@
         <v>0</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C82" s="1">
         <v>13</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E82" s="1">
         <v>0</v>
@@ -3576,21 +3823,21 @@
         <v>0</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C83" s="1">
         <v>14</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E83" s="1">
         <v>0</v>
@@ -3599,21 +3846,21 @@
         <v>0</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C84" s="1">
         <v>15</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E84" s="1">
         <v>0</v>
@@ -3622,21 +3869,21 @@
         <v>0</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C85" s="1">
         <v>16</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E85" s="1">
         <v>0</v>
@@ -3645,21 +3892,21 @@
         <v>0</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C86" s="1">
         <v>17</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E86" s="1">
         <v>0</v>
@@ -3668,21 +3915,21 @@
         <v>0</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C87" s="1">
         <v>18</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E87" s="1">
         <v>0</v>
@@ -3691,21 +3938,21 @@
         <v>0</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C88" s="1">
         <v>19</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E88" s="1">
         <v>0</v>
@@ -3714,21 +3961,21 @@
         <v>0</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C89" s="1">
         <v>20</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E89" s="1">
         <v>0</v>
@@ -3737,21 +3984,21 @@
         <v>0</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C90" s="1">
         <v>21</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E90" s="1">
         <v>0</v>
@@ -3760,21 +4007,21 @@
         <v>0</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C91" s="1">
         <v>22</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E91" s="1">
         <v>0</v>
@@ -3783,21 +4030,21 @@
         <v>0</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C92" s="1">
         <v>23</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E92" s="1">
         <v>0</v>
@@ -3806,21 +4053,21 @@
         <v>0</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C93" s="1">
         <v>24</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E93" s="1">
         <v>0</v>
@@ -3829,21 +4076,21 @@
         <v>0</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C94" s="1">
         <v>25</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E94" s="1">
         <v>0</v>
@@ -3852,21 +4099,21 @@
         <v>0</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C95" s="1">
         <v>26</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E95" s="1">
         <v>0</v>
@@ -3875,7 +4122,7 @@
         <v>0</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -3904,331 +4151,331 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C2" s="1">
         <v>44</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C3" s="1">
         <v>45</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C4" s="1">
         <v>46</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C5" s="1">
         <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C6" s="1">
         <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C7" s="1">
         <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C8" s="1">
         <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C9" s="1">
         <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C10" s="1">
         <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C11" s="1">
         <v>45</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C12" s="1">
         <v>45</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C13" s="1">
         <v>45</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H13" s="1"/>
     </row>

--- a/Program/Datos/datos_manuales.xlsx
+++ b/Program/Datos/datos_manuales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mhoyosme\Desktop\Proyecto\Program\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D62192-68A2-48DB-9119-0E82294732E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF89A593-B5FD-42A7-8B6D-5AB7283AC40F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{CD6D87B3-3E85-4D9D-BFF0-D4E802493E81}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="198">
   <si>
     <t>75.0</t>
   </si>
@@ -627,6 +627,12 @@
   </si>
   <si>
     <t>Fusible PDB2 B</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>DC</t>
   </si>
 </sst>
 </file>
@@ -739,34 +745,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="39">
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="40">
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1146,6 +1125,36 @@
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1160,64 +1169,65 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5874A6EA-08E4-4C13-B67C-CB816184D3C0}" name="Tabla2" displayName="Tabla2" ref="A1:G2" totalsRowShown="0" headerRowDxfId="38" dataDxfId="36" headerRowBorderDxfId="37" tableBorderDxfId="35" totalsRowBorderDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5874A6EA-08E4-4C13-B67C-CB816184D3C0}" name="Tabla2" displayName="Tabla2" ref="A1:G2" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26" totalsRowBorderDxfId="25">
   <autoFilter ref="A1:G2" xr:uid="{5874A6EA-08E4-4C13-B67C-CB816184D3C0}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{9F2439FA-30A1-4D90-9F47-A866995AD462}" name="nombre_nodo" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{E1FDA295-F988-4715-B9C7-42286712743D}" name="tipo" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{E955F37D-B353-4F7A-9521-F49CF205229C}" name="codigo" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{22F231D9-9879-4122-9BAF-253B8C04BB15}" name="regional" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{CA56A5C1-DCFB-45F9-A91D-E19FDCFDDF4C}" name="direccion" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{42241B89-6C4C-4F8D-8BF0-C33F36C93C1D}" name="capacidad_kva" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{96DBA14E-72BF-4616-A90F-5169ACCA998C}" name="voltaje_sistema_dc" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{9F2439FA-30A1-4D90-9F47-A866995AD462}" name="nombre_nodo" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{E1FDA295-F988-4715-B9C7-42286712743D}" name="tipo" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{E955F37D-B353-4F7A-9521-F49CF205229C}" name="codigo" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{22F231D9-9879-4122-9BAF-253B8C04BB15}" name="regional" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{CA56A5C1-DCFB-45F9-A91D-E19FDCFDDF4C}" name="direccion" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{42241B89-6C4C-4F8D-8BF0-C33F36C93C1D}" name="capacidad_kva" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{96DBA14E-72BF-4616-A90F-5169ACCA998C}" name="voltaje_sistema_dc" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2E5421E9-2724-423C-851B-A0845D404EE3}" name="Tabla3" displayName="Tabla3" ref="A1:F15" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
-  <autoFilter ref="A1:F15" xr:uid="{2E5421E9-2724-423C-851B-A0845D404EE3}"/>
-  <tableColumns count="6">
-    <tableColumn id="7" xr3:uid="{4DA03894-7D07-44E5-BB0D-94373ECA9338}" name="ubicacion" dataDxfId="24"/>
-    <tableColumn id="1" xr3:uid="{FEF86DC1-CDF6-4D2B-9711-3CE2E8FDC61D}" name="componente" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{E8898F3B-F793-4C03-9ADB-3E0756FDECAF}" name="marca" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{E4F60FA1-A5C6-4AC3-BF15-A364399D1E4E}" name="referencia" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{CD65DA30-5B1A-4E7C-8023-7B23F0D22BDF}" name="capacidad_amps" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{00B2E6A4-9D0B-4CA9-A4F2-C6F8CCF0A7FC}" name="calibre_cable_awg" dataDxfId="19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2E5421E9-2724-423C-851B-A0845D404EE3}" name="Tabla3" displayName="Tabla3" ref="A1:G15" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+  <autoFilter ref="A1:G15" xr:uid="{2E5421E9-2724-423C-851B-A0845D404EE3}"/>
+  <tableColumns count="7">
+    <tableColumn id="7" xr3:uid="{4DA03894-7D07-44E5-BB0D-94373ECA9338}" name="ubicacion" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{FEF86DC1-CDF6-4D2B-9711-3CE2E8FDC61D}" name="componente" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{E8898F3B-F793-4C03-9ADB-3E0756FDECAF}" name="marca" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{E4F60FA1-A5C6-4AC3-BF15-A364399D1E4E}" name="referencia" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{CD65DA30-5B1A-4E7C-8023-7B23F0D22BDF}" name="capacidad_amps" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{EC182694-78B3-42C0-947F-3CB1555CB945}" name="tipo" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{00B2E6A4-9D0B-4CA9-A4F2-C6F8CCF0A7FC}" name="calibre_cable_awg" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4F279930-8CE0-4458-A500-A4804307D033}" name="Tabla4" displayName="Tabla4" ref="A1:G95" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4F279930-8CE0-4458-A500-A4804307D033}" name="Tabla4" displayName="Tabla4" ref="A1:G95" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="A1:G95" xr:uid="{4F279930-8CE0-4458-A500-A4804307D033}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{6CBBC484-43B4-4212-8A72-72C36A0AA59A}" name="pdb_nombre" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{E0A6FC31-B215-4C57-B8C0-A8E53A5B832B}" name="fuente" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{4F3E6BCE-4115-4327-9F4D-9FE1AB222BE1}" name="posicion" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{0F488469-BA24-4436-842B-6D2F9F8F4214}" name="estado" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{DAED4AB6-F7E7-4C43-9177-F8900C29D95C}" name="capacidad" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{59F7B2D4-6A80-447C-B8ED-E0F301A44C2C}" name="corriente" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{DCE97B5A-FEBD-4BAD-9EB4-7754B346D6AB}" name="equipo_refencia" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{6CBBC484-43B4-4212-8A72-72C36A0AA59A}" name="pdb_nombre" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{E0A6FC31-B215-4C57-B8C0-A8E53A5B832B}" name="fuente" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{4F3E6BCE-4115-4327-9F4D-9FE1AB222BE1}" name="posicion" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{0F488469-BA24-4436-842B-6D2F9F8F4214}" name="estado" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{DAED4AB6-F7E7-4C43-9177-F8900C29D95C}" name="capacidad" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{59F7B2D4-6A80-447C-B8ED-E0F301A44C2C}" name="corriente" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{DCE97B5A-FEBD-4BAD-9EB4-7754B346D6AB}" name="equipo_refencia" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DE2280A1-9E4C-4DCD-BF7E-888FBA537ECA}" name="Tabla1" displayName="Tabla1" ref="A1:H13" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowCellStyle="Normal" dataCellStyle="Normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DE2280A1-9E4C-4DCD-BF7E-888FBA537ECA}" name="Tabla1" displayName="Tabla1" ref="A1:H13" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38" headerRowCellStyle="Normal" dataCellStyle="Normal">
   <autoFilter ref="A1:H13" xr:uid="{DE2280A1-9E4C-4DCD-BF7E-888FBA537ECA}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{3AB90701-9B35-41AA-99FD-EA000C0FBAC6}" name="nombre_rack" dataDxfId="7" dataCellStyle="Normal"/>
-    <tableColumn id="10" xr3:uid="{552625CA-FFA9-4D0F-9AE4-8E8AA2CFD81A}" name="Label" dataDxfId="6" dataCellStyle="Normal"/>
-    <tableColumn id="4" xr3:uid="{4E5A4E54-6DE7-48C8-8A66-7C97E2FA04A1}" name="u_totales" dataDxfId="5" dataCellStyle="Normal"/>
-    <tableColumn id="11" xr3:uid="{BE625927-AF15-478E-87C9-1BC144738D1C}" name="Espacio" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{D32C66C7-BCD4-4610-8774-1CC22DE4F9A0}" name="u_ocupadas_listado" dataDxfId="3" dataCellStyle="Normal"/>
-    <tableColumn id="6" xr3:uid="{282C4EE8-ED53-4C8B-B914-B33DF7A75E4D}" name="u_libres_listado" dataDxfId="2" dataCellStyle="Normal"/>
-    <tableColumn id="7" xr3:uid="{D325EA4D-3855-4FB8-8337-3E9BBFFDA68B}" name="nombre_foto" dataDxfId="1" dataCellStyle="Normal"/>
-    <tableColumn id="8" xr3:uid="{94BF02C2-1F70-4B1B-94F9-F73DDBFA1E1A}" name="Detalle_rack" dataDxfId="0" dataCellStyle="Normal"/>
+    <tableColumn id="1" xr3:uid="{3AB90701-9B35-41AA-99FD-EA000C0FBAC6}" name="nombre_rack" dataDxfId="37" dataCellStyle="Normal"/>
+    <tableColumn id="10" xr3:uid="{552625CA-FFA9-4D0F-9AE4-8E8AA2CFD81A}" name="Label" dataDxfId="36" dataCellStyle="Normal"/>
+    <tableColumn id="4" xr3:uid="{4E5A4E54-6DE7-48C8-8A66-7C97E2FA04A1}" name="u_totales" dataDxfId="35" dataCellStyle="Normal"/>
+    <tableColumn id="11" xr3:uid="{BE625927-AF15-478E-87C9-1BC144738D1C}" name="Espacio" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{D32C66C7-BCD4-4610-8774-1CC22DE4F9A0}" name="u_ocupadas_listado" dataDxfId="33" dataCellStyle="Normal"/>
+    <tableColumn id="6" xr3:uid="{282C4EE8-ED53-4C8B-B914-B33DF7A75E4D}" name="u_libres_listado" dataDxfId="32" dataCellStyle="Normal"/>
+    <tableColumn id="7" xr3:uid="{D325EA4D-3855-4FB8-8337-3E9BBFFDA68B}" name="nombre_foto" dataDxfId="31" dataCellStyle="Normal"/>
+    <tableColumn id="8" xr3:uid="{94BF02C2-1F70-4B1B-94F9-F73DDBFA1E1A}" name="Detalle_rack" dataDxfId="30" dataCellStyle="Normal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1607,7 +1617,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70FE85F0-6249-49C0-98C3-75140ABDEF17}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.85546875" customWidth="1"/>
@@ -1618,7 +1628,7 @@
     <col min="6" max="6" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>99</v>
       </c>
@@ -1635,10 +1645,13 @@
         <v>92</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>82</v>
       </c>
@@ -1655,10 +1668,13 @@
         <v>200</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>82</v>
       </c>
@@ -1674,11 +1690,14 @@
       <c r="E3" s="1">
         <v>400</v>
       </c>
-      <c r="F3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F3" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>82</v>
       </c>
@@ -1694,11 +1713,14 @@
       <c r="E4" s="1">
         <v>400</v>
       </c>
-      <c r="F4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F4" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>81</v>
       </c>
@@ -1714,13 +1736,16 @@
       <c r="E5" s="1">
         <v>225</v>
       </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F5" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>19</v>
@@ -1735,12 +1760,15 @@
         <v>125</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>20</v>
@@ -1755,10 +1783,13 @@
         <v>125</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>83</v>
       </c>
@@ -1774,11 +1805,14 @@
       <c r="E8" s="1">
         <v>500</v>
       </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F8" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>83</v>
       </c>
@@ -1794,11 +1828,14 @@
       <c r="E9" s="1">
         <v>500</v>
       </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F9" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>84</v>
       </c>
@@ -1814,11 +1851,14 @@
       <c r="E10" s="1">
         <v>500</v>
       </c>
-      <c r="F10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F10" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>84</v>
       </c>
@@ -1834,11 +1874,14 @@
       <c r="E11" s="1">
         <v>500</v>
       </c>
-      <c r="F11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F11" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
@@ -1854,11 +1897,14 @@
       <c r="E12" s="1">
         <v>150</v>
       </c>
-      <c r="F12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F12" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -1874,11 +1920,14 @@
       <c r="E13" s="1">
         <v>150</v>
       </c>
-      <c r="F13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F13" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
@@ -1894,11 +1943,14 @@
       <c r="E14" s="1">
         <v>250</v>
       </c>
-      <c r="F14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F14" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -1914,7 +1966,10 @@
       <c r="E15" s="1">
         <v>250</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G15" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Program/Datos/datos_manuales.xlsx
+++ b/Program/Datos/datos_manuales.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mhoyosme\Desktop\Proyecto\Program\Datos\DB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mhoyosme\Desktop\Proyecto\Program\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A5E04C5-3996-4A06-8583-2776110EE807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A089F8-FCE2-474C-9EB8-54691CB96B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{CD6D87B3-3E85-4D9D-BFF0-D4E802493E81}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CD6D87B3-3E85-4D9D-BFF0-D4E802493E81}"/>
   </bookViews>
   <sheets>
     <sheet name="info_nodo" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="201">
   <si>
     <t>75.0</t>
   </si>
@@ -630,6 +630,18 @@
   </si>
   <si>
     <t>fecha_actualizacion</t>
+  </si>
+  <si>
+    <t>racks_fila1</t>
+  </si>
+  <si>
+    <t>maximo_fila1</t>
+  </si>
+  <si>
+    <t>racks_fila2</t>
+  </si>
+  <si>
+    <t>maximo_fila2</t>
   </si>
 </sst>
 </file>
@@ -762,18 +774,63 @@
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="45">
+  <dxfs count="49">
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -798,7 +855,13 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1097,6 +1160,25 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <border outline="0">
         <top style="thin">
           <color theme="4" tint="0.39997558519241921"/>
@@ -1180,6 +1262,12 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1217,70 +1305,74 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5874A6EA-08E4-4C13-B67C-CB816184D3C0}" name="Tabla2" displayName="Tabla2" ref="A1:I2" totalsRowShown="0" headerRowDxfId="35" dataDxfId="33" headerRowBorderDxfId="34" tableBorderDxfId="32" totalsRowBorderDxfId="31">
-  <autoFilter ref="A1:I2" xr:uid="{5874A6EA-08E4-4C13-B67C-CB816184D3C0}"/>
-  <tableColumns count="9">
-    <tableColumn id="9" xr3:uid="{CECA8E98-26C0-4163-8468-2AF801D0011A}" name="fecha_actualizacion" dataDxfId="4"/>
-    <tableColumn id="1" xr3:uid="{9F2439FA-30A1-4D90-9F47-A866995AD462}" name="nombre_nodo" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{E1FDA295-F988-4715-B9C7-42286712743D}" name="tipo" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{E955F37D-B353-4F7A-9521-F49CF205229C}" name="codigo" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{22F231D9-9879-4122-9BAF-253B8C04BB15}" name="regional" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{CA56A5C1-DCFB-45F9-A91D-E19FDCFDDF4C}" name="direccion" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{42241B89-6C4C-4F8D-8BF0-C33F36C93C1D}" name="capacidad_kva" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{56027613-F328-4A47-854A-A7351A040A78}" name="Racks" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{E4373386-BBF6-4449-9671-65FBEB1E22FC}" name="maximo_racks" dataDxfId="23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5874A6EA-08E4-4C13-B67C-CB816184D3C0}" name="Tabla2" displayName="Tabla2" ref="A1:M2" totalsRowShown="0" headerRowDxfId="37" dataDxfId="35" headerRowBorderDxfId="36" tableBorderDxfId="34" totalsRowBorderDxfId="33">
+  <autoFilter ref="A1:M2" xr:uid="{5874A6EA-08E4-4C13-B67C-CB816184D3C0}"/>
+  <tableColumns count="13">
+    <tableColumn id="9" xr3:uid="{CECA8E98-26C0-4163-8468-2AF801D0011A}" name="fecha_actualizacion" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{9F2439FA-30A1-4D90-9F47-A866995AD462}" name="nombre_nodo" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{E1FDA295-F988-4715-B9C7-42286712743D}" name="tipo" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{E955F37D-B353-4F7A-9521-F49CF205229C}" name="codigo" dataDxfId="29"/>
+    <tableColumn id="7" xr3:uid="{22F231D9-9879-4122-9BAF-253B8C04BB15}" name="regional" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{CA56A5C1-DCFB-45F9-A91D-E19FDCFDDF4C}" name="direccion" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{42241B89-6C4C-4F8D-8BF0-C33F36C93C1D}" name="capacidad_kva" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{56027613-F328-4A47-854A-A7351A040A78}" name="Racks" dataDxfId="25"/>
+    <tableColumn id="13" xr3:uid="{BB3E5E1E-67D5-411D-9660-223ED91BCE77}" name="racks_fila1" dataDxfId="0"/>
+    <tableColumn id="12" xr3:uid="{4A299800-601E-4F05-A381-3AEFA8EA6235}" name="maximo_fila1" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{59A27D18-90FB-4FFB-A6B8-0D2CEAAFE4B1}" name="racks_fila2" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{4868B7F1-AFE0-466B-B7EE-159C1ADACD28}" name="maximo_fila2" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{E4373386-BBF6-4449-9671-65FBEB1E22FC}" name="maximo_racks" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2E5421E9-2724-423C-851B-A0845D404EE3}" name="Tabla3" displayName="Tabla3" ref="A1:H15" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2E5421E9-2724-423C-851B-A0845D404EE3}" name="Tabla3" displayName="Tabla3" ref="A1:H15" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
   <autoFilter ref="A1:H15" xr:uid="{2E5421E9-2724-423C-851B-A0845D404EE3}"/>
   <tableColumns count="8">
-    <tableColumn id="8" xr3:uid="{ABDE68D5-1580-4EC3-99DE-1CDD2718510E}" name="fecha_actualizacion" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{4DA03894-7D07-44E5-BB0D-94373ECA9338}" name="ubicacion" dataDxfId="42"/>
-    <tableColumn id="1" xr3:uid="{FEF86DC1-CDF6-4D2B-9711-3CE2E8FDC61D}" name="componente" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{E8898F3B-F793-4C03-9ADB-3E0756FDECAF}" name="marca" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{E4F60FA1-A5C6-4AC3-BF15-A364399D1E4E}" name="referencia" dataDxfId="39"/>
-    <tableColumn id="4" xr3:uid="{CD65DA30-5B1A-4E7C-8023-7B23F0D22BDF}" name="capacidad_amps" dataDxfId="38"/>
-    <tableColumn id="6" xr3:uid="{EC182694-78B3-42C0-947F-3CB1555CB945}" name="tipo" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{00B2E6A4-9D0B-4CA9-A4F2-C6F8CCF0A7FC}" name="calibre_cable_salida" dataDxfId="36"/>
+    <tableColumn id="8" xr3:uid="{ABDE68D5-1580-4EC3-99DE-1CDD2718510E}" name="fecha_actualizacion" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{4DA03894-7D07-44E5-BB0D-94373ECA9338}" name="ubicacion" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{FEF86DC1-CDF6-4D2B-9711-3CE2E8FDC61D}" name="componente" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{E8898F3B-F793-4C03-9ADB-3E0756FDECAF}" name="marca" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{E4F60FA1-A5C6-4AC3-BF15-A364399D1E4E}" name="referencia" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{CD65DA30-5B1A-4E7C-8023-7B23F0D22BDF}" name="capacidad_amps" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{EC182694-78B3-42C0-947F-3CB1555CB945}" name="tipo" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{00B2E6A4-9D0B-4CA9-A4F2-C6F8CCF0A7FC}" name="calibre_cable_salida" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4F279930-8CE0-4458-A500-A4804307D033}" name="Tabla4" displayName="Tabla4" ref="A1:H95" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4F279930-8CE0-4458-A500-A4804307D033}" name="Tabla4" displayName="Tabla4" ref="A1:H95" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
   <autoFilter ref="A1:H95" xr:uid="{4F279930-8CE0-4458-A500-A4804307D033}"/>
   <tableColumns count="8">
-    <tableColumn id="8" xr3:uid="{C6E15445-B3AA-4D36-9C70-D5CC6DB7C7AF}" name="fecha_actualizacion" dataDxfId="1"/>
-    <tableColumn id="1" xr3:uid="{6CBBC484-43B4-4212-8A72-72C36A0AA59A}" name="pdb_nombre" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{E0A6FC31-B215-4C57-B8C0-A8E53A5B832B}" name="fuente" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{4F3E6BCE-4115-4327-9F4D-9FE1AB222BE1}" name="posicion" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{0F488469-BA24-4436-842B-6D2F9F8F4214}" name="estado" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{DAED4AB6-F7E7-4C43-9177-F8900C29D95C}" name="capacidad" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{59F7B2D4-6A80-447C-B8ED-E0F301A44C2C}" name="corriente" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{DCE97B5A-FEBD-4BAD-9EB4-7754B346D6AB}" name="equipo_refencia" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{C6E15445-B3AA-4D36-9C70-D5CC6DB7C7AF}" name="fecha_actualizacion" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{6CBBC484-43B4-4212-8A72-72C36A0AA59A}" name="pdb_nombre" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{E0A6FC31-B215-4C57-B8C0-A8E53A5B832B}" name="fuente" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{4F3E6BCE-4115-4327-9F4D-9FE1AB222BE1}" name="posicion" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{0F488469-BA24-4436-842B-6D2F9F8F4214}" name="estado" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{DAED4AB6-F7E7-4C43-9177-F8900C29D95C}" name="capacidad" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{59F7B2D4-6A80-447C-B8ED-E0F301A44C2C}" name="corriente" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{DCE97B5A-FEBD-4BAD-9EB4-7754B346D6AB}" name="equipo_refencia" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DE2280A1-9E4C-4DCD-BF7E-888FBA537ECA}" name="Tabla1" displayName="Tabla1" ref="A1:I13" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" headerRowCellStyle="Normal" dataCellStyle="Normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DE2280A1-9E4C-4DCD-BF7E-888FBA537ECA}" name="Tabla1" displayName="Tabla1" ref="A1:I13" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47" headerRowCellStyle="Normal" dataCellStyle="Normal">
   <autoFilter ref="A1:I13" xr:uid="{DE2280A1-9E4C-4DCD-BF7E-888FBA537ECA}"/>
   <tableColumns count="9">
-    <tableColumn id="2" xr3:uid="{FD967790-1272-4A59-B055-7255D7DEC2B4}" name="fecha_actualizacion" dataDxfId="0"/>
-    <tableColumn id="1" xr3:uid="{3AB90701-9B35-41AA-99FD-EA000C0FBAC6}" name="nombre_rack" dataDxfId="12" dataCellStyle="Normal"/>
-    <tableColumn id="10" xr3:uid="{552625CA-FFA9-4D0F-9AE4-8E8AA2CFD81A}" name="Label" dataDxfId="11" dataCellStyle="Normal"/>
-    <tableColumn id="4" xr3:uid="{4E5A4E54-6DE7-48C8-8A66-7C97E2FA04A1}" name="u_totales" dataDxfId="10" dataCellStyle="Normal"/>
-    <tableColumn id="11" xr3:uid="{BE625927-AF15-478E-87C9-1BC144738D1C}" name="Espacio" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{D32C66C7-BCD4-4610-8774-1CC22DE4F9A0}" name="u_ocupadas_listado" dataDxfId="8" dataCellStyle="Normal"/>
-    <tableColumn id="6" xr3:uid="{282C4EE8-ED53-4C8B-B914-B33DF7A75E4D}" name="u_libres_listado" dataDxfId="7" dataCellStyle="Normal"/>
-    <tableColumn id="7" xr3:uid="{D325EA4D-3855-4FB8-8337-3E9BBFFDA68B}" name="nombre_foto" dataDxfId="6" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="8" xr3:uid="{94BF02C2-1F70-4B1B-94F9-F73DDBFA1E1A}" name="Detalle_rack" dataDxfId="5" dataCellStyle="Normal"/>
+    <tableColumn id="2" xr3:uid="{FD967790-1272-4A59-B055-7255D7DEC2B4}" name="fecha_actualizacion" dataDxfId="46"/>
+    <tableColumn id="1" xr3:uid="{3AB90701-9B35-41AA-99FD-EA000C0FBAC6}" name="nombre_rack" dataDxfId="45" dataCellStyle="Normal"/>
+    <tableColumn id="10" xr3:uid="{552625CA-FFA9-4D0F-9AE4-8E8AA2CFD81A}" name="Label" dataDxfId="44" dataCellStyle="Normal"/>
+    <tableColumn id="4" xr3:uid="{4E5A4E54-6DE7-48C8-8A66-7C97E2FA04A1}" name="u_totales" dataDxfId="43" dataCellStyle="Normal"/>
+    <tableColumn id="11" xr3:uid="{BE625927-AF15-478E-87C9-1BC144738D1C}" name="Espacio" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{D32C66C7-BCD4-4610-8774-1CC22DE4F9A0}" name="u_ocupadas_listado" dataDxfId="41" dataCellStyle="Normal"/>
+    <tableColumn id="6" xr3:uid="{282C4EE8-ED53-4C8B-B914-B33DF7A75E4D}" name="u_libres_listado" dataDxfId="40" dataCellStyle="Normal"/>
+    <tableColumn id="7" xr3:uid="{D325EA4D-3855-4FB8-8337-3E9BBFFDA68B}" name="nombre_foto" dataDxfId="39" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="8" xr3:uid="{94BF02C2-1F70-4B1B-94F9-F73DDBFA1E1A}" name="Detalle_rack" dataDxfId="38" dataCellStyle="Normal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1604,7 +1696,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D621632-B9CB-4A1F-AF18-E08B1244778C}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.7109375" customWidth="1"/>
@@ -1612,12 +1704,12 @@
     <col min="5" max="5" width="20.140625" customWidth="1"/>
     <col min="6" max="6" width="31.42578125" customWidth="1"/>
     <col min="7" max="7" width="39.42578125" customWidth="1"/>
-    <col min="8" max="8" width="18.85546875" customWidth="1"/>
-    <col min="9" max="9" width="23.28515625" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" customWidth="1"/>
+    <col min="8" max="12" width="18.85546875" customWidth="1"/>
+    <col min="13" max="13" width="23.28515625" customWidth="1"/>
+    <col min="14" max="14" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>196</v>
       </c>
@@ -1643,10 +1735,22 @@
         <v>189</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
         <v>46087.387627314813</v>
       </c>
@@ -1672,6 +1776,18 @@
         <v>11</v>
       </c>
       <c r="I2" s="3">
+        <v>4</v>
+      </c>
+      <c r="J2" s="3">
+        <v>6</v>
+      </c>
+      <c r="K2" s="3">
+        <v>8</v>
+      </c>
+      <c r="L2" s="3">
+        <v>10</v>
+      </c>
+      <c r="M2" s="3">
         <v>16</v>
       </c>
     </row>

--- a/Program/Datos/datos_manuales.xlsx
+++ b/Program/Datos/datos_manuales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mhoyosme\Desktop\Proyecto\Program\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A089F8-FCE2-474C-9EB8-54691CB96B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5A33B9-6648-49C3-ADFB-E0AF533BD72B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CD6D87B3-3E85-4D9D-BFF0-D4E802493E81}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="202">
   <si>
     <t>75.0</t>
   </si>
@@ -642,6 +642,9 @@
   </si>
   <si>
     <t>maximo_fila2</t>
+  </si>
+  <si>
+    <t>1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39,40, 41, 42, 43, 44, 45</t>
   </si>
 </sst>
 </file>
@@ -776,6 +779,99 @@
   </cellStyles>
   <dxfs count="49">
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="4" tint="0.79998168889431442"/>
@@ -850,66 +946,6 @@
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -1258,39 +1294,6 @@
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1305,74 +1308,74 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5874A6EA-08E4-4C13-B67C-CB816184D3C0}" name="Tabla2" displayName="Tabla2" ref="A1:M2" totalsRowShown="0" headerRowDxfId="37" dataDxfId="35" headerRowBorderDxfId="36" tableBorderDxfId="34" totalsRowBorderDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5874A6EA-08E4-4C13-B67C-CB816184D3C0}" name="Tabla2" displayName="Tabla2" ref="A1:M2" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45" totalsRowBorderDxfId="44">
   <autoFilter ref="A1:M2" xr:uid="{5874A6EA-08E4-4C13-B67C-CB816184D3C0}"/>
   <tableColumns count="13">
-    <tableColumn id="9" xr3:uid="{CECA8E98-26C0-4163-8468-2AF801D0011A}" name="fecha_actualizacion" dataDxfId="32"/>
-    <tableColumn id="1" xr3:uid="{9F2439FA-30A1-4D90-9F47-A866995AD462}" name="nombre_nodo" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{E1FDA295-F988-4715-B9C7-42286712743D}" name="tipo" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{E955F37D-B353-4F7A-9521-F49CF205229C}" name="codigo" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{22F231D9-9879-4122-9BAF-253B8C04BB15}" name="regional" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{CA56A5C1-DCFB-45F9-A91D-E19FDCFDDF4C}" name="direccion" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{42241B89-6C4C-4F8D-8BF0-C33F36C93C1D}" name="capacidad_kva" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{56027613-F328-4A47-854A-A7351A040A78}" name="Racks" dataDxfId="25"/>
-    <tableColumn id="13" xr3:uid="{BB3E5E1E-67D5-411D-9660-223ED91BCE77}" name="racks_fila1" dataDxfId="0"/>
-    <tableColumn id="12" xr3:uid="{4A299800-601E-4F05-A381-3AEFA8EA6235}" name="maximo_fila1" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{59A27D18-90FB-4FFB-A6B8-0D2CEAAFE4B1}" name="racks_fila2" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{4868B7F1-AFE0-466B-B7EE-159C1ADACD28}" name="maximo_fila2" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{E4373386-BBF6-4449-9671-65FBEB1E22FC}" name="maximo_racks" dataDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{CECA8E98-26C0-4163-8468-2AF801D0011A}" name="fecha_actualizacion" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{9F2439FA-30A1-4D90-9F47-A866995AD462}" name="nombre_nodo" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{E1FDA295-F988-4715-B9C7-42286712743D}" name="tipo" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{E955F37D-B353-4F7A-9521-F49CF205229C}" name="codigo" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{22F231D9-9879-4122-9BAF-253B8C04BB15}" name="regional" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{CA56A5C1-DCFB-45F9-A91D-E19FDCFDDF4C}" name="direccion" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{42241B89-6C4C-4F8D-8BF0-C33F36C93C1D}" name="capacidad_kva" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{56027613-F328-4A47-854A-A7351A040A78}" name="Racks" dataDxfId="36"/>
+    <tableColumn id="13" xr3:uid="{BB3E5E1E-67D5-411D-9660-223ED91BCE77}" name="racks_fila1" dataDxfId="35"/>
+    <tableColumn id="12" xr3:uid="{4A299800-601E-4F05-A381-3AEFA8EA6235}" name="maximo_fila1" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{59A27D18-90FB-4FFB-A6B8-0D2CEAAFE4B1}" name="racks_fila2" dataDxfId="33"/>
+    <tableColumn id="10" xr3:uid="{4868B7F1-AFE0-466B-B7EE-159C1ADACD28}" name="maximo_fila2" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{E4373386-BBF6-4449-9671-65FBEB1E22FC}" name="maximo_racks" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2E5421E9-2724-423C-851B-A0845D404EE3}" name="Tabla3" displayName="Tabla3" ref="A1:H15" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2E5421E9-2724-423C-851B-A0845D404EE3}" name="Tabla3" displayName="Tabla3" ref="A1:H15" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:H15" xr:uid="{2E5421E9-2724-423C-851B-A0845D404EE3}"/>
   <tableColumns count="8">
-    <tableColumn id="8" xr3:uid="{ABDE68D5-1580-4EC3-99DE-1CDD2718510E}" name="fecha_actualizacion" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{4DA03894-7D07-44E5-BB0D-94373ECA9338}" name="ubicacion" dataDxfId="20"/>
-    <tableColumn id="1" xr3:uid="{FEF86DC1-CDF6-4D2B-9711-3CE2E8FDC61D}" name="componente" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{E8898F3B-F793-4C03-9ADB-3E0756FDECAF}" name="marca" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{E4F60FA1-A5C6-4AC3-BF15-A364399D1E4E}" name="referencia" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{CD65DA30-5B1A-4E7C-8023-7B23F0D22BDF}" name="capacidad_amps" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{EC182694-78B3-42C0-947F-3CB1555CB945}" name="tipo" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{00B2E6A4-9D0B-4CA9-A4F2-C6F8CCF0A7FC}" name="calibre_cable_salida" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{ABDE68D5-1580-4EC3-99DE-1CDD2718510E}" name="fecha_actualizacion" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{4DA03894-7D07-44E5-BB0D-94373ECA9338}" name="ubicacion" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{FEF86DC1-CDF6-4D2B-9711-3CE2E8FDC61D}" name="componente" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{E8898F3B-F793-4C03-9ADB-3E0756FDECAF}" name="marca" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{E4F60FA1-A5C6-4AC3-BF15-A364399D1E4E}" name="referencia" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{CD65DA30-5B1A-4E7C-8023-7B23F0D22BDF}" name="capacidad_amps" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{EC182694-78B3-42C0-947F-3CB1555CB945}" name="tipo" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{00B2E6A4-9D0B-4CA9-A4F2-C6F8CCF0A7FC}" name="calibre_cable_salida" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4F279930-8CE0-4458-A500-A4804307D033}" name="Tabla4" displayName="Tabla4" ref="A1:H95" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4F279930-8CE0-4458-A500-A4804307D033}" name="Tabla4" displayName="Tabla4" ref="A1:H95" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <autoFilter ref="A1:H95" xr:uid="{4F279930-8CE0-4458-A500-A4804307D033}"/>
   <tableColumns count="8">
-    <tableColumn id="8" xr3:uid="{C6E15445-B3AA-4D36-9C70-D5CC6DB7C7AF}" name="fecha_actualizacion" dataDxfId="11"/>
-    <tableColumn id="1" xr3:uid="{6CBBC484-43B4-4212-8A72-72C36A0AA59A}" name="pdb_nombre" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{E0A6FC31-B215-4C57-B8C0-A8E53A5B832B}" name="fuente" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{4F3E6BCE-4115-4327-9F4D-9FE1AB222BE1}" name="posicion" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{0F488469-BA24-4436-842B-6D2F9F8F4214}" name="estado" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{DAED4AB6-F7E7-4C43-9177-F8900C29D95C}" name="capacidad" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{59F7B2D4-6A80-447C-B8ED-E0F301A44C2C}" name="corriente" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{DCE97B5A-FEBD-4BAD-9EB4-7754B346D6AB}" name="equipo_refencia" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{C6E15445-B3AA-4D36-9C70-D5CC6DB7C7AF}" name="fecha_actualizacion" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{6CBBC484-43B4-4212-8A72-72C36A0AA59A}" name="pdb_nombre" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{E0A6FC31-B215-4C57-B8C0-A8E53A5B832B}" name="fuente" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{4F3E6BCE-4115-4327-9F4D-9FE1AB222BE1}" name="posicion" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{0F488469-BA24-4436-842B-6D2F9F8F4214}" name="estado" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{DAED4AB6-F7E7-4C43-9177-F8900C29D95C}" name="capacidad" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{59F7B2D4-6A80-447C-B8ED-E0F301A44C2C}" name="corriente" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{DCE97B5A-FEBD-4BAD-9EB4-7754B346D6AB}" name="equipo_refencia" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DE2280A1-9E4C-4DCD-BF7E-888FBA537ECA}" name="Tabla1" displayName="Tabla1" ref="A1:I13" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47" headerRowCellStyle="Normal" dataCellStyle="Normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DE2280A1-9E4C-4DCD-BF7E-888FBA537ECA}" name="Tabla1" displayName="Tabla1" ref="A1:I13" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" headerRowCellStyle="Normal" dataCellStyle="Normal">
   <autoFilter ref="A1:I13" xr:uid="{DE2280A1-9E4C-4DCD-BF7E-888FBA537ECA}"/>
   <tableColumns count="9">
-    <tableColumn id="2" xr3:uid="{FD967790-1272-4A59-B055-7255D7DEC2B4}" name="fecha_actualizacion" dataDxfId="46"/>
-    <tableColumn id="1" xr3:uid="{3AB90701-9B35-41AA-99FD-EA000C0FBAC6}" name="nombre_rack" dataDxfId="45" dataCellStyle="Normal"/>
-    <tableColumn id="10" xr3:uid="{552625CA-FFA9-4D0F-9AE4-8E8AA2CFD81A}" name="Label" dataDxfId="44" dataCellStyle="Normal"/>
-    <tableColumn id="4" xr3:uid="{4E5A4E54-6DE7-48C8-8A66-7C97E2FA04A1}" name="u_totales" dataDxfId="43" dataCellStyle="Normal"/>
-    <tableColumn id="11" xr3:uid="{BE625927-AF15-478E-87C9-1BC144738D1C}" name="Espacio" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{D32C66C7-BCD4-4610-8774-1CC22DE4F9A0}" name="u_ocupadas_listado" dataDxfId="41" dataCellStyle="Normal"/>
-    <tableColumn id="6" xr3:uid="{282C4EE8-ED53-4C8B-B914-B33DF7A75E4D}" name="u_libres_listado" dataDxfId="40" dataCellStyle="Normal"/>
-    <tableColumn id="7" xr3:uid="{D325EA4D-3855-4FB8-8337-3E9BBFFDA68B}" name="nombre_foto" dataDxfId="39" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="8" xr3:uid="{94BF02C2-1F70-4B1B-94F9-F73DDBFA1E1A}" name="Detalle_rack" dataDxfId="38" dataCellStyle="Normal"/>
+    <tableColumn id="2" xr3:uid="{FD967790-1272-4A59-B055-7255D7DEC2B4}" name="fecha_actualizacion" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{3AB90701-9B35-41AA-99FD-EA000C0FBAC6}" name="nombre_rack" dataDxfId="7" dataCellStyle="Normal"/>
+    <tableColumn id="10" xr3:uid="{552625CA-FFA9-4D0F-9AE4-8E8AA2CFD81A}" name="Label" dataDxfId="6" dataCellStyle="Normal"/>
+    <tableColumn id="4" xr3:uid="{4E5A4E54-6DE7-48C8-8A66-7C97E2FA04A1}" name="u_totales" dataDxfId="5" dataCellStyle="Normal"/>
+    <tableColumn id="11" xr3:uid="{BE625927-AF15-478E-87C9-1BC144738D1C}" name="Espacio" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{D32C66C7-BCD4-4610-8774-1CC22DE4F9A0}" name="u_ocupadas_listado" dataDxfId="3" dataCellStyle="Normal"/>
+    <tableColumn id="6" xr3:uid="{282C4EE8-ED53-4C8B-B914-B33DF7A75E4D}" name="u_libres_listado" dataDxfId="2" dataCellStyle="Normal"/>
+    <tableColumn id="7" xr3:uid="{D325EA4D-3855-4FB8-8337-3E9BBFFDA68B}" name="nombre_foto" dataDxfId="1" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="8" xr3:uid="{94BF02C2-1F70-4B1B-94F9-F73DDBFA1E1A}" name="Detalle_rack" dataDxfId="0" dataCellStyle="Normal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4720,7 +4723,7 @@
     <col min="1" max="2" width="18.140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="34.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="60" style="1" customWidth="1"/>
     <col min="7" max="7" width="119.28515625" style="1" customWidth="1"/>
     <col min="8" max="8" width="106.42578125" style="1" customWidth="1"/>
     <col min="9" max="10" width="255.5703125" customWidth="1"/>
@@ -5088,10 +5091,13 @@
         <v>45</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>129</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>179</v>
